--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1382,6 +1382,899 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129147416</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nisses kärr, Nisses kärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>524903</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6540272</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129148106</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nisses kärr, Nisses kärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>525044</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6540148</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129145546</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nisses kärr, Nisses kärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>524608</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6540443</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129145502</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nisses kärr, Nisses kärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>524608</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6540443</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129147810</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58093</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nisses kärr, Nisses kärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>525053</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6540188</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129147862</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nisses kärr, Nisses kärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>525053</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6540188</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129147178</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nisses kärr, Nisses kärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>524777</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6540451</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129148009</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nisses kärr, Nisses kärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>525044</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6540148</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1492,17 +1492,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
+          <t>Barbro Fehrm Friberg, Per Arneborn, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129148106</v>
+        <v>129145546</v>
       </c>
       <c r="B9" t="n">
-        <v>92849</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,46 +1510,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525044</v>
+        <v>524608</v>
       </c>
       <c r="R9" t="n">
-        <v>6540148</v>
+        <v>6540443</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129145546</v>
+        <v>129148106</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>92854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,37 +1617,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524608</v>
+        <v>525044</v>
       </c>
       <c r="R10" t="n">
-        <v>6540443</v>
+        <v>6540148</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129147416</v>
+        <v>129148106</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>92857</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,45 +1395,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524903</v>
+        <v>525044</v>
       </c>
       <c r="R8" t="n">
-        <v>6540272</v>
+        <v>6540148</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,7 +1463,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1473,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,22 +1488,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Per Arneborn, Lotta Sörman</t>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129145546</v>
+        <v>129147416</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,37 +1511,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524608</v>
+        <v>524903</v>
       </c>
       <c r="R9" t="n">
-        <v>6540443</v>
+        <v>6540272</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,22 +1603,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129148106</v>
+        <v>129145546</v>
       </c>
       <c r="B10" t="n">
-        <v>92854</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,46 +1626,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525044</v>
+        <v>524608</v>
       </c>
       <c r="R10" t="n">
-        <v>6540148</v>
+        <v>6540443</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129148106</v>
+        <v>129147416</v>
       </c>
       <c r="B8" t="n">
-        <v>92857</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,46 +1395,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525044</v>
+        <v>524903</v>
       </c>
       <c r="R8" t="n">
-        <v>6540148</v>
+        <v>6540272</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1473,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,22 +1487,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129147416</v>
+        <v>129148106</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>92857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,45 +1510,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524903</v>
+        <v>525044</v>
       </c>
       <c r="R9" t="n">
-        <v>6540272</v>
+        <v>6540148</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129147416</v>
+        <v>129148106</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>92864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,45 +1395,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524903</v>
+        <v>525044</v>
       </c>
       <c r="R8" t="n">
-        <v>6540272</v>
+        <v>6540148</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,7 +1463,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1473,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,22 +1488,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129148106</v>
+        <v>129147416</v>
       </c>
       <c r="B9" t="n">
-        <v>92857</v>
+        <v>57722</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,46 +1511,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525044</v>
+        <v>524903</v>
       </c>
       <c r="R9" t="n">
-        <v>6540148</v>
+        <v>6540272</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
         <v>129145546</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>129145502</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129147810</v>
       </c>
       <c r="B12" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129147862</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129147178</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129148009</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>129148106</v>
       </c>
       <c r="B8" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129148106</v>
+        <v>129147416</v>
       </c>
       <c r="B8" t="n">
-        <v>92871</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,46 +1395,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525044</v>
+        <v>524903</v>
       </c>
       <c r="R8" t="n">
-        <v>6540148</v>
+        <v>6540272</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1473,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,22 +1487,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129147416</v>
+        <v>129148106</v>
       </c>
       <c r="B9" t="n">
-        <v>57722</v>
+        <v>92873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,45 +1510,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524903</v>
+        <v>525044</v>
       </c>
       <c r="R9" t="n">
-        <v>6540272</v>
+        <v>6540148</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
         <v>129145546</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>129145502</v>
       </c>
       <c r="B11" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129147810</v>
       </c>
       <c r="B12" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129147862</v>
       </c>
       <c r="B13" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129147178</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129148009</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129147416</v>
+        <v>129145546</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,45 +1395,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524903</v>
+        <v>524608</v>
       </c>
       <c r="R8" t="n">
-        <v>6540272</v>
+        <v>6540443</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,12 +1479,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1615,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129145546</v>
+        <v>129147416</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,37 +1618,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524608</v>
+        <v>524903</v>
       </c>
       <c r="R10" t="n">
-        <v>6540443</v>
+        <v>6540272</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,12 +1710,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129145546</v>
+        <v>129148106</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>92859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,37 +1395,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524608</v>
+        <v>525044</v>
       </c>
       <c r="R8" t="n">
-        <v>6540443</v>
+        <v>6540148</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1463,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1473,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129148106</v>
+        <v>129147416</v>
       </c>
       <c r="B9" t="n">
-        <v>92873</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,46 +1511,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525044</v>
+        <v>524903</v>
       </c>
       <c r="R9" t="n">
-        <v>6540148</v>
+        <v>6540272</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,22 +1603,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129147416</v>
+        <v>129145546</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,45 +1626,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524903</v>
+        <v>524608</v>
       </c>
       <c r="R10" t="n">
-        <v>6540272</v>
+        <v>6540443</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,12 +1710,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129148106</v>
+        <v>129147416</v>
       </c>
       <c r="B8" t="n">
-        <v>92859</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,46 +1395,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525044</v>
+        <v>524903</v>
       </c>
       <c r="R8" t="n">
-        <v>6540148</v>
+        <v>6540272</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1473,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,22 +1487,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129147416</v>
+        <v>129148106</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>92860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,45 +1510,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524903</v>
+        <v>525044</v>
       </c>
       <c r="R9" t="n">
-        <v>6540272</v>
+        <v>6540148</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129147416</v>
+        <v>129148106</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>92860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,45 +1395,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524903</v>
+        <v>525044</v>
       </c>
       <c r="R8" t="n">
-        <v>6540272</v>
+        <v>6540148</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,7 +1463,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1473,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,22 +1488,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
+          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129148106</v>
+        <v>129147416</v>
       </c>
       <c r="B9" t="n">
-        <v>92860</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,46 +1511,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nisses kärr, Nisses kärr, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525044</v>
+        <v>524903</v>
       </c>
       <c r="R9" t="n">
-        <v>6540148</v>
+        <v>6540272</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Barbro Fehrm Friberg</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 60559-2020 artfynd.xlsx
+++ b/artfynd/A 60559-2020 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>129148106</v>
       </c>
       <c r="B8" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
